--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/RogueCard.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/RogueCard.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="198">
   <si>
     <t>##var</t>
   </si>
@@ -104,55 +104,13 @@
     <t>隐藏tags</t>
   </si>
   <si>
-    <t>迅捷步伐</t>
-  </si>
-  <si>
-    <t>获得一层迅捷效果，提高作战机动性。</t>
-  </si>
-  <si>
-    <t>rogue_speed_1</t>
-  </si>
-  <si>
-    <t>buff:200111</t>
-  </si>
-  <si>
-    <t>51,52</t>
-  </si>
-  <si>
-    <t>1,2</t>
-  </si>
-  <si>
-    <t>猎手步频</t>
-  </si>
-  <si>
-    <t>获得一层迅捷效果，适合持续拉扯与追击。</t>
-  </si>
-  <si>
-    <t>rogue_speed_2</t>
-  </si>
-  <si>
-    <t>53</t>
-  </si>
-  <si>
-    <t>战术加速</t>
-  </si>
-  <si>
-    <t>获得一层迅捷效果，用于快速切入或脱离战场。</t>
-  </si>
-  <si>
-    <t>rogue_speed_3</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
     <t>金主驾到</t>
   </si>
   <si>
     <t>地图出现一个商人，靠近交互后获得30000金币。</t>
   </si>
   <si>
-    <t>rogue_gold_1</t>
+    <t>export (18)_0</t>
   </si>
   <si>
     <t>buff:1001</t>
@@ -167,7 +125,7 @@
     <t>直接给予5000金币。</t>
   </si>
   <si>
-    <t>rogue_gold_2</t>
+    <t>export (18)_1</t>
   </si>
   <si>
     <t>buff:1002</t>
@@ -179,7 +137,7 @@
     <t>每击杀一个怪物额外获得300金币。</t>
   </si>
   <si>
-    <t>rogue_gold_3</t>
+    <t>export (18)_2</t>
   </si>
   <si>
     <t>buff:1003</t>
@@ -191,7 +149,7 @@
     <t>受到致命伤害时，消耗当前携带金币的50%来免疫本次伤害。</t>
   </si>
   <si>
-    <t>rogue_gold_4</t>
+    <t>export (18)_3</t>
   </si>
   <si>
     <t>buff:1004</t>
@@ -203,19 +161,19 @@
     <t>每次开启物资箱未获得高品质物品，额外获得300金币。</t>
   </si>
   <si>
-    <t>rogue_gold_5</t>
+    <t>export (18)_4</t>
   </si>
   <si>
     <t>buff:1005</t>
   </si>
   <si>
-    <t>财富即力量</t>
+    <t>以钱服人</t>
   </si>
   <si>
     <t>身上每携带500金币，提升1%的全伤害。</t>
   </si>
   <si>
-    <t>rogue_gold_6</t>
+    <t>export (18)_5</t>
   </si>
   <si>
     <t>buff:1006</t>
@@ -227,7 +185,7 @@
     <t>每次进入一个从未到过的区域，立即获得800金币。</t>
   </si>
   <si>
-    <t>rogue_gold_7</t>
+    <t>export (18)_6</t>
   </si>
   <si>
     <t>buff:1007</t>
@@ -239,7 +197,7 @@
     <t>每隔20秒扫描一次，在小地图上高亮显示半径30米内所有未搜索的箱子。</t>
   </si>
   <si>
-    <t>rogue_search_1</t>
+    <t>export (18)_7</t>
   </si>
   <si>
     <t>buff:1011</t>
@@ -254,19 +212,19 @@
     <t>搜索区域开出宝箱的概率大幅度增加。</t>
   </si>
   <si>
-    <t>rogue_search_2</t>
+    <t>export (18)_8</t>
   </si>
   <si>
     <t>buff:1012</t>
   </si>
   <si>
-    <t>紫色钥匙</t>
+    <t>临时权限</t>
   </si>
   <si>
     <t>获得一个临时的紫色钥匙。</t>
   </si>
   <si>
-    <t>rogue_search_3</t>
+    <t>export (18)_9</t>
   </si>
   <si>
     <t>buff:1013</t>
@@ -276,27 +234,32 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>允许你在</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="Aptos Narrow"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>3</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>米外通过交互键直接搜索容器，无需贴脸。</t>
     </r>
   </si>
   <si>
-    <t>rogue_search_4</t>
+    <t>export (18)_10</t>
   </si>
   <si>
     <t>buff:1014</t>
@@ -308,7 +271,7 @@
     <t>搜索动作完全不发出声音。</t>
   </si>
   <si>
-    <t>rogue_search_5</t>
+    <t>export (18)_11</t>
   </si>
   <si>
     <t>buff:1015</t>
@@ -320,7 +283,7 @@
     <t>背包空间越满，临时生命增幅越高。</t>
   </si>
   <si>
-    <t>rogue_search_6</t>
+    <t>export (18)_12</t>
   </si>
   <si>
     <t>buff:1016</t>
@@ -332,7 +295,7 @@
     <t>任务：击杀15个怪物后，对怪物的伤害增加50%。</t>
   </si>
   <si>
-    <t>rogue_boss_1</t>
+    <t>export (18)_13</t>
   </si>
   <si>
     <t>buff:1021</t>
@@ -345,67 +308,72 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+      </rPr>
       <t>Boss</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>对你的伤害降低</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="Aptos Narrow"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>30%</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>，对</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="Aptos Narrow"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>Boss</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>造成伤害获得</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="Aptos Narrow"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>30%</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>吸血效果。</t>
     </r>
   </si>
   <si>
-    <t>rogue_boss_2</t>
+    <t>export (18)_14</t>
   </si>
   <si>
     <t>buff:1022</t>
@@ -417,7 +385,7 @@
     <t>击杀怪物后回复2%的已损生命值。</t>
   </si>
   <si>
-    <t>rogue_boss_3</t>
+    <t>export (18)_15</t>
   </si>
   <si>
     <t>buff:1023</t>
@@ -429,7 +397,7 @@
     <t>搜索区域开出怪物的概率大幅度增加。</t>
   </si>
   <si>
-    <t>rogue_boss_4</t>
+    <t>export (18)_16</t>
   </si>
   <si>
     <t>buff:1024</t>
@@ -441,7 +409,7 @@
     <t>击杀精英怪或Boss后，主武器获得永久穿透和伤害附魔。</t>
   </si>
   <si>
-    <t>rogue_boss_5</t>
+    <t>export (18)_17</t>
   </si>
   <si>
     <t>buff:1025</t>
@@ -456,7 +424,7 @@
     <t>向30米内的怪物移动时，速度提高30%。</t>
   </si>
   <si>
-    <t>rogue_boss_6</t>
+    <t>export (18)_18</t>
   </si>
   <si>
     <t>buff:1026</t>
@@ -468,7 +436,7 @@
     <t>枪械的攻击距离提高20%。</t>
   </si>
   <si>
-    <t>rogue_fire_1</t>
+    <t>export (18)_19</t>
   </si>
   <si>
     <t>buff:1031</t>
@@ -483,7 +451,7 @@
     <t>你的技能无法使用，枪械的攻击速度提高50%。</t>
   </si>
   <si>
-    <t>rogue_fire_2</t>
+    <t>export (18)_20</t>
   </si>
   <si>
     <t>buff:1032</t>
@@ -493,27 +461,32 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>枪械命中敌方英雄时，本局临时获得</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="Aptos Narrow"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>1%</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
         <rFont val="宋体"/>
         <charset val="134"/>
-        <sz val="11"/>
       </rPr>
       <t>暴击率。</t>
     </r>
   </si>
   <si>
-    <t>rogue_fire_3</t>
+    <t>export (18)_21</t>
   </si>
   <si>
     <t>buff:1033</t>
@@ -525,7 +498,7 @@
     <t>枪械弹匣容量提升50%，换弹速度提高30%。</t>
   </si>
   <si>
-    <t>rogue_fire_4</t>
+    <t>export (18)_22</t>
   </si>
   <si>
     <t>buff:1034</t>
@@ -537,7 +510,7 @@
     <t>静止不动5秒以上，每射击15发子弹随机抛射一个陷阱。</t>
   </si>
   <si>
-    <t>rogue_fire_5</t>
+    <t>export (18)_23</t>
   </si>
   <si>
     <t>buff:1035</t>
@@ -549,7 +522,7 @@
     <t>每次换弹后，前3发子弹伤害提升200%并附带穿透效果。</t>
   </si>
   <si>
-    <t>rogue_fire_6</t>
+    <t>export (18)_24</t>
   </si>
   <si>
     <t>buff:1036</t>
@@ -561,7 +534,7 @@
     <t>体型变大，生命值增加30%。</t>
   </si>
   <si>
-    <t>rogue_endure_1</t>
+    <t>export (18)_25</t>
   </si>
   <si>
     <t>buff:1041</t>
@@ -570,13 +543,13 @@
     <t>105</t>
   </si>
   <si>
-    <t>生命涌泉</t>
+    <t>活性细胞</t>
   </si>
   <si>
     <t>每秒恢复1%最大生命值。</t>
   </si>
   <si>
-    <t>rogue_endure_2</t>
+    <t>export (18)_26</t>
   </si>
   <si>
     <t>buff:1042</t>
@@ -588,7 +561,7 @@
     <t>生命值低于20%时，获得一个相当于50%最大生命值的护盾。</t>
   </si>
   <si>
-    <t>rogue_endure_3</t>
+    <t>export (18)_27</t>
   </si>
   <si>
     <t>buff:1043</t>
@@ -600,19 +573,19 @@
     <t>游戏延长5分钟，每30秒生命上限增加3%。</t>
   </si>
   <si>
-    <t>rogue_endure_4</t>
+    <t>export (19)_0</t>
   </si>
   <si>
     <t>buff:1044</t>
   </si>
   <si>
-    <t>绿树精灵</t>
+    <t>森之呼唤</t>
   </si>
   <si>
     <t>每30秒召唤一个绿树精灵为你恢复生命。</t>
   </si>
   <si>
-    <t>rogue_endure_5</t>
+    <t>export (19)_1</t>
   </si>
   <si>
     <t>buff:1045</t>
@@ -624,7 +597,7 @@
     <t>对生命值低于30%的目标额外造成30%伤害。</t>
   </si>
   <si>
-    <t>rogue_hunter_1</t>
+    <t>export (19)_2</t>
   </si>
   <si>
     <t>buff:1051</t>
@@ -639,7 +612,7 @@
     <t>每次击杀叠加30%攻击力，最多3层。</t>
   </si>
   <si>
-    <t>rogue_hunter_2</t>
+    <t>export (19)_3</t>
   </si>
   <si>
     <t>buff:1052</t>
@@ -651,19 +624,35 @@
     <t>脱离战斗后进入隐身状态。</t>
   </si>
   <si>
-    <t>rogue_hunter_3</t>
+    <t>export (19)_4</t>
   </si>
   <si>
     <t>buff:1053</t>
   </si>
   <si>
-    <t>灵巧身形</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>绝地短刀</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Aptos Narrow"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
   <si>
     <t>体型变小，移动速度提高30%，体型差越大伤害越高。</t>
   </si>
   <si>
-    <t>rogue_hunter_4</t>
+    <t>export (19)_5</t>
   </si>
   <si>
     <t>buff:1054</t>
@@ -675,7 +664,7 @@
     <t>攻击距离降低80%，但伤害提升400%。</t>
   </si>
   <si>
-    <t>rogue_hunter_5</t>
+    <t>export (19)_8</t>
   </si>
   <si>
     <t>buff:1055</t>
@@ -690,7 +679,7 @@
     <t>释放技能后获得10%移动速度加成。</t>
   </si>
   <si>
-    <t>rogue_hunter_6</t>
+    <t>export (19)_10</t>
   </si>
   <si>
     <t>buff:1056</t>
@@ -702,7 +691,7 @@
     <t>获得1个随机紫色卡牌。</t>
   </si>
   <si>
-    <t>rogue_dice_1</t>
+    <t>export (19)_11</t>
   </si>
   <si>
     <t>buff:1061</t>
@@ -717,19 +706,19 @@
     <t>获得2个随机橙色卡牌。</t>
   </si>
   <si>
-    <t>rogue_dice_2</t>
+    <t>export (19)_12</t>
   </si>
   <si>
     <t>buff:1062</t>
   </si>
   <si>
-    <t>一击必杀</t>
+    <t>金色奇迹</t>
   </si>
   <si>
     <t>1%概率秒杀非Boss目标，爆出8888金币。</t>
   </si>
   <si>
-    <t>rogue_dice_3</t>
+    <t>export (19)_13</t>
   </si>
   <si>
     <t>buff:1063</t>
@@ -741,19 +730,19 @@
     <t>所有概率触发效果的触发率提升50%。</t>
   </si>
   <si>
-    <t>rogue_dice_4</t>
+    <t>export (19)_14</t>
   </si>
   <si>
     <t>buff:1064</t>
   </si>
   <si>
-    <t>命运重置</t>
+    <t>命运洗牌</t>
   </si>
   <si>
     <t>移除所有已选卡牌，替换为2张随机紫色和1张随机橙色卡牌。</t>
   </si>
   <si>
-    <t>rogue_dice_5</t>
+    <t>export (19)_15</t>
   </si>
   <si>
     <t>buff:1065</t>
@@ -769,13 +758,19 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <name val="Aptos Narrow"/>
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1234,164 +1229,162 @@
     </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="2" applyFont="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="3" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="4" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="2" applyFont="0" fillId="2" applyFill="1" borderId="1" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="5" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="6" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="7" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="8" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="9" applyFont="1" fillId="0" applyFill="0" borderId="2" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="3" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="10" applyFont="1" fillId="0" applyFill="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="11" applyFont="1" fillId="3" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="12" applyFont="1" fillId="4" applyFill="1" borderId="5" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="13" applyFont="1" fillId="4" applyFill="1" borderId="4" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="14" applyFont="1" fillId="5" applyFill="1" borderId="6" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="15" applyFont="1" fillId="0" applyFill="0" borderId="7" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="16" applyFont="1" fillId="0" applyFill="0" borderId="8" applyBorder="1" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="17" applyFont="1" fillId="6" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="18" applyFont="1" fillId="7" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="19" applyFont="1" fillId="8" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="9" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="10" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="11" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="12" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="13" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="14" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="15" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="16" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="17" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="18" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="19" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="20" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="21" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="22" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="23" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="24" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="25" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="26" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="27" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="28" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="29" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="30" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="21" applyFont="1" fillId="31" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" applyNumberFormat="0" fontId="20" applyFont="1" fillId="32" applyFill="1" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" applyFill="0" borderId="0" applyBorder="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1444,7 +1437,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="41">
+  <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1635,336 +1628,28 @@
         </bottom>
       </border>
     </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color theme="4"/>
-        </left>
-        <right style="thin">
-          <color theme="4"/>
-        </right>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-        <horizontal style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="double">
-          <color theme="4"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.799981688894314"/>
-          <bgColor theme="4" tint="0.799981688894314"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.399975585192419"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="29"/>
-      <tableStyleElement type="headerRow" dxfId="30"/>
-      <tableStyleElement type="totalRow" dxfId="31"/>
-      <tableStyleElement type="firstColumn" dxfId="32"/>
-      <tableStyleElement type="lastColumn" dxfId="32"/>
-      <tableStyleElement type="firstRowStripe" dxfId="33"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="33"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="34"/>
-      <tableStyleElement type="totalRow" dxfId="35"/>
-      <tableStyleElement type="firstRowStripe" dxfId="33"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="33"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="36"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="32"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="37"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="38"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="39"/>
-      <tableStyleElement type="pageFieldValues" dxfId="40"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -2231,9 +1916,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="3" max="3" width="10.8583333333333" customWidth="1"/>
@@ -2243,7 +1928,7 @@
     <col min="9" max="10" width="15.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2265,17 +1950,17 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="0" t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="0" t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="0" t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
@@ -2297,7 +1982,7 @@
       <c r="G2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="2" t="s">
@@ -2307,7 +1992,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -2318,7 +2003,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
     </row>
-    <row r="4" ht="69.75">
+    <row r="4" ht="30" customHeight="1" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
@@ -2343,599 +2028,596 @@
       <c r="H4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1">
-        <v>1</v>
-      </c>
-      <c r="C5" s="4" t="s">
+    <row r="5" spans="1:10">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G5" s="1">
-        <v>100</v>
-      </c>
-      <c r="H5" s="0">
-        <v>1</v>
+      <c r="G5">
+        <v>80</v>
+      </c>
+      <c r="H5">
+        <v>2</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>29</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1">
+      <c r="D6" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="G6">
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G7">
+        <v>80</v>
+      </c>
+      <c r="H7">
         <v>2</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="1">
+      <c r="I7" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8">
+        <v>60</v>
+      </c>
+      <c r="H8">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G9">
+        <v>80</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="G10">
+        <v>80</v>
+      </c>
+      <c r="H10">
+        <v>2</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G11">
+        <v>80</v>
+      </c>
+      <c r="H11">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="B12">
+        <v>1011</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12">
         <v>100</v>
       </c>
-      <c r="H6" s="0">
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="B13">
+        <v>1012</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G13">
+        <v>80</v>
+      </c>
+      <c r="H13">
         <v>2</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1">
+      <c r="I13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="B14">
+        <v>1013</v>
+      </c>
+      <c r="C14" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G14">
+        <v>80</v>
+      </c>
+      <c r="H14">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="B15">
+        <v>1014</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G15">
+        <v>60</v>
+      </c>
+      <c r="H15">
         <v>3</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G7" s="1">
+      <c r="I15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="B16">
+        <v>1015</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G16">
+        <v>80</v>
+      </c>
+      <c r="H16">
+        <v>2</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
+      <c r="B17">
+        <v>1016</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17">
+        <v>60</v>
+      </c>
+      <c r="H17">
+        <v>3</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10">
+      <c r="B18">
+        <v>1021</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18">
+        <v>60</v>
+      </c>
+      <c r="H18">
+        <v>3</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10">
+      <c r="B19">
+        <v>1022</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G19">
+        <v>80</v>
+      </c>
+      <c r="H19">
+        <v>2</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
+      <c r="B20">
+        <v>1023</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G20">
         <v>100</v>
       </c>
-      <c r="H7" s="0">
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
+      <c r="B21">
+        <v>1024</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G21">
+        <v>80</v>
+      </c>
+      <c r="H21">
+        <v>2</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
+      <c r="B22">
+        <v>1025</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G22">
+        <v>60</v>
+      </c>
+      <c r="H22">
         <v>3</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="0">
-        <v>1001</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="G8" s="0">
+      <c r="I22" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
+      <c r="B23">
+        <v>1026</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="G23">
+        <v>100</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="24" spans="2:10">
+      <c r="B24">
+        <v>1031</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="G24">
         <v>80</v>
       </c>
-      <c r="H8" s="0">
+      <c r="H24">
         <v>2</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="0">
-        <v>1002</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="G9" s="0">
-        <v>100</v>
-      </c>
-      <c r="H9" s="0">
-        <v>1</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="0">
-        <v>1003</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="0">
-        <v>80</v>
-      </c>
-      <c r="H10" s="0">
-        <v>2</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="0">
-        <v>1004</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="G11" s="0">
-        <v>60</v>
-      </c>
-      <c r="H11" s="0">
-        <v>3</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="0">
-        <v>1005</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="0">
-        <v>80</v>
-      </c>
-      <c r="H12" s="0">
-        <v>2</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="0">
-        <v>1006</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G13" s="0">
-        <v>80</v>
-      </c>
-      <c r="H13" s="0">
-        <v>2</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="0">
-        <v>1007</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="G14" s="0">
-        <v>80</v>
-      </c>
-      <c r="H14" s="0">
-        <v>2</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="0">
-        <v>1011</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="G15" s="0">
-        <v>100</v>
-      </c>
-      <c r="H15" s="0">
-        <v>1</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="0">
-        <v>1012</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="0">
-        <v>80</v>
-      </c>
-      <c r="H16" s="0">
-        <v>2</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="0">
-        <v>1013</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="G17" s="0">
-        <v>80</v>
-      </c>
-      <c r="H17" s="0">
-        <v>2</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="0">
-        <v>1014</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G18" s="0">
-        <v>60</v>
-      </c>
-      <c r="H18" s="0">
-        <v>3</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="0">
-        <v>1015</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="G19" s="0">
-        <v>80</v>
-      </c>
-      <c r="H19" s="0">
-        <v>2</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="0">
-        <v>1016</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="0">
-        <v>60</v>
-      </c>
-      <c r="H20" s="0">
-        <v>3</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="0">
-        <v>1021</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="0">
-        <v>60</v>
-      </c>
-      <c r="H21" s="0">
-        <v>3</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="0">
-        <v>1022</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="G22" s="0">
-        <v>80</v>
-      </c>
-      <c r="H22" s="0">
-        <v>2</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="0">
-        <v>1023</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="G23" s="0">
-        <v>100</v>
-      </c>
-      <c r="H23" s="0">
-        <v>1</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="0">
-        <v>1024</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="I24" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="G24" s="0">
-        <v>80</v>
-      </c>
-      <c r="H24" s="0">
-        <v>2</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="J24" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="B25" s="0">
-        <v>1025</v>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
+      <c r="B25">
+        <v>1032</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>110</v>
@@ -2949,486 +2631,486 @@
       <c r="F25" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="G25" s="0">
+      <c r="G25">
         <v>60</v>
       </c>
-      <c r="H25" s="0">
+      <c r="H25">
         <v>3</v>
       </c>
       <c r="I25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="26" spans="2:10">
+      <c r="B26">
+        <v>1033</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="J25" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="0">
-        <v>1026</v>
-      </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="G26">
+        <v>60</v>
+      </c>
+      <c r="H26">
+        <v>3</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
+      <c r="B27">
+        <v>1034</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="G26" s="0">
+      <c r="D27" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G27">
         <v>100</v>
       </c>
-      <c r="H26" s="0">
+      <c r="H27">
         <v>1</v>
       </c>
-      <c r="I26" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="0">
-        <v>1031</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="I27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
+      <c r="B28">
+        <v>1035</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G27" s="0">
+      <c r="D28" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G28">
         <v>80</v>
       </c>
-      <c r="H27" s="0">
+      <c r="H28">
         <v>2</v>
       </c>
-      <c r="I27" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="B28" s="0">
-        <v>1032</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="I28" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="29" spans="2:10">
+      <c r="B29">
+        <v>1036</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="G28" s="0">
+      <c r="E29" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G29">
+        <v>80</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
+      <c r="B30">
+        <v>1041</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G30">
+        <v>80</v>
+      </c>
+      <c r="H30">
+        <v>2</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="2:10">
+      <c r="B31">
+        <v>1042</v>
+      </c>
+      <c r="C31" t="s">
+        <v>135</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G31">
+        <v>80</v>
+      </c>
+      <c r="H31">
+        <v>2</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
+      <c r="B32">
+        <v>1043</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G32">
         <v>60</v>
       </c>
-      <c r="H28" s="0">
+      <c r="H32">
         <v>3</v>
       </c>
-      <c r="I28" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="0">
-        <v>1033</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="G29" s="0">
+      <c r="I32" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="33" spans="2:10">
+      <c r="B33">
+        <v>1044</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G33">
         <v>60</v>
       </c>
-      <c r="H29" s="0">
+      <c r="H33">
         <v>3</v>
       </c>
-      <c r="I29" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="0">
-        <v>1034</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="I33" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G30" s="0">
+      <c r="J33" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34">
+        <v>1045</v>
+      </c>
+      <c r="C34" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="G34">
+        <v>60</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35">
+        <v>1051</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G35">
+        <v>80</v>
+      </c>
+      <c r="H35">
+        <v>2</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
+      <c r="B36">
+        <v>1052</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G36">
+        <v>60</v>
+      </c>
+      <c r="H36">
+        <v>3</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="B37">
+        <v>1053</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G37">
+        <v>60</v>
+      </c>
+      <c r="H37">
+        <v>3</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="B38">
+        <v>1054</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="G38">
+        <v>80</v>
+      </c>
+      <c r="H38">
+        <v>2</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="B39">
+        <v>1055</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="G39">
+        <v>60</v>
+      </c>
+      <c r="H39">
+        <v>3</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
+      <c r="B40">
+        <v>1056</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G40">
         <v>100</v>
       </c>
-      <c r="H30" s="0">
+      <c r="H40">
         <v>1</v>
       </c>
-      <c r="I30" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="B31" s="0">
-        <v>1035</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G31" s="0">
-        <v>80</v>
-      </c>
-      <c r="H31" s="0">
-        <v>2</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="0">
-        <v>1036</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G32" s="0">
-        <v>80</v>
-      </c>
-      <c r="H32" s="0">
-        <v>2</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="0">
-        <v>1041</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G33" s="0">
-        <v>80</v>
-      </c>
-      <c r="H33" s="0">
-        <v>2</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="0">
-        <v>1042</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G34" s="0">
-        <v>80</v>
-      </c>
-      <c r="H34" s="0">
-        <v>2</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J34" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="0">
-        <v>1043</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" s="2" t="s">
+      <c r="I40" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="G35" s="0">
-        <v>60</v>
-      </c>
-      <c r="H35" s="0">
-        <v>3</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J35" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="0">
-        <v>1044</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="G36" s="0">
-        <v>60</v>
-      </c>
-      <c r="H36" s="0">
-        <v>3</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" s="0">
-        <v>1045</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="G37" s="0">
-        <v>60</v>
-      </c>
-      <c r="H37" s="0">
-        <v>3</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="J37" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="0">
-        <v>1051</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="G38" s="0">
-        <v>80</v>
-      </c>
-      <c r="H38" s="0">
-        <v>2</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J38" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="0">
-        <v>1052</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F39" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="G39" s="0">
-        <v>60</v>
-      </c>
-      <c r="H39" s="0">
-        <v>3</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J39" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="0">
-        <v>1053</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="F40" s="2" t="s">
+      <c r="J40" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41">
+        <v>1061</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="G40" s="0">
-        <v>60</v>
-      </c>
-      <c r="H40" s="0">
-        <v>3</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="0">
-        <v>1054</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="D41" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="F41" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="F41" s="2" t="s">
+      <c r="G41">
+        <v>100</v>
+      </c>
+      <c r="H41">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="G41" s="0">
-        <v>80</v>
-      </c>
-      <c r="H41" s="0">
-        <v>2</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="J41" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="0">
-        <v>1055</v>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42">
+        <v>1062</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>182</v>
@@ -3442,200 +3124,123 @@
       <c r="F42" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="G42" s="0">
+      <c r="G42">
         <v>60</v>
       </c>
-      <c r="H42" s="0">
+      <c r="H42">
         <v>3</v>
       </c>
       <c r="I42" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="43" spans="2:10">
+      <c r="B43">
+        <v>1063</v>
+      </c>
+      <c r="C43" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="J42" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="B43" s="0">
-        <v>1056</v>
-      </c>
-      <c r="C43" s="2" t="s">
+      <c r="D43" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="F43" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="G43">
+        <v>60</v>
+      </c>
+      <c r="H43">
+        <v>3</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
+      <c r="B44">
+        <v>1064</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="G43" s="0">
-        <v>100</v>
-      </c>
-      <c r="H43" s="0">
-        <v>1</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="J43" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="B44" s="0">
-        <v>1061</v>
-      </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F44" s="2" t="s">
+      <c r="G44">
+        <v>80</v>
+      </c>
+      <c r="H44">
+        <v>2</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="45" spans="2:10">
+      <c r="B45">
+        <v>1065</v>
+      </c>
+      <c r="C45" t="s">
         <v>194</v>
       </c>
-      <c r="G44" s="0">
-        <v>100</v>
-      </c>
-      <c r="H44" s="0">
-        <v>1</v>
-      </c>
-      <c r="I44" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="J44" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="B45" s="0">
-        <v>1062</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="E45" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="F45" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F45" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="G45" s="0">
+      <c r="G45">
         <v>60</v>
       </c>
-      <c r="H45" s="0">
+      <c r="H45">
         <v>3</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>195</v>
+        <v>181</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="B46" s="0">
-        <v>1063</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="G46" s="0">
-        <v>60</v>
-      </c>
-      <c r="H46" s="0">
-        <v>3</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="B47" s="0">
-        <v>1064</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F47" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G47" s="0">
-        <v>80</v>
-      </c>
-      <c r="H47" s="0">
-        <v>2</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="J47" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="B48" s="0">
-        <v>1065</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="G48" s="0">
-        <v>60</v>
-      </c>
-      <c r="H48" s="0">
-        <v>3</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="J48" s="2" t="s">
-        <v>195</v>
-      </c>
+        <v>181</v>
+      </c>
+    </row>
+    <row r="49" spans="5:5">
+      <c r="E49" s="2"/>
+    </row>
+    <row r="50" spans="5:5">
+      <c r="E50" s="2"/>
+    </row>
+    <row r="51" spans="5:5">
+      <c r="E51" s="2"/>
+    </row>
+    <row r="52" spans="5:5">
+      <c r="E52" s="2"/>
+    </row>
+    <row r="53" spans="5:5">
+      <c r="E53" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/RogueCard.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/RogueCard.xlsx
@@ -1924,8 +1924,9 @@
     <col min="3" max="3" width="10.8583333333333" customWidth="1"/>
     <col min="4" max="4" width="67.375" customWidth="1"/>
     <col min="5" max="5" width="14.425" customWidth="1"/>
-    <col min="6" max="6" width="11.7083333333333" customWidth="1"/>
+    <col min="6" max="6" width="23.875" customWidth="1"/>
     <col min="9" max="10" width="15.25" customWidth="1"/>
+    <col min="12" max="12" width="12.625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
